--- a/variations/Camden/V0.2.2/BOM-SPARC-Camden-V0.2.2.xlsx
+++ b/variations/Camden/V0.2.2/BOM-SPARC-Camden-V0.2.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34105aa9bb97034c/Documents/GitHub/Smart-Pack-for-Advanced-Research-and-Control/variations/Camden/V0.2.1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Smart-Pack-for-Advanced-Research-and-Control\variations\Camden\V0.2.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CA57DAE7-B8DB-4790-BE80-4BF5B52EAE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA887D42-8906-4263-A679-6314E660A737}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C02FDF-E677-4CCF-B93B-DF51A371EF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="174">
   <si>
     <t>Total Cost</t>
   </si>
@@ -525,6 +525,39 @@
   </si>
   <si>
     <t>https://shop.micro-measurements.com/my_cart_item_list.php?v_cat_code=STRESS_ANALYSIS_STRAIN_GAGE</t>
+  </si>
+  <si>
+    <t>NI-9209 with D-sub (783729-01)</t>
+  </si>
+  <si>
+    <t>NI Analog Voltage in</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/ni/783729-01/15219085</t>
+  </si>
+  <si>
+    <t>https://www.ni.com/en/shop/hardware/voltage/model-ni-9209?srsltid=AfmBOor7Lxlk-Bc63Rm3pHBdRV0FkdxyXFu65pzzLkmQPxDcSqa-YH_y#783729-01</t>
+  </si>
+  <si>
+    <t>https://www.newark.com/ni/783729-01/ni-9209-voltage-input-module-24bit/dp/13AJ4083</t>
+  </si>
+  <si>
+    <t>Dsub connector</t>
+  </si>
+  <si>
+    <t>Amphenol ICC (FCI) D37S13A6GX00LF</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/amphenol-cs-fci/D37S13A6GX00LF/1538196</t>
+  </si>
+  <si>
+    <t>Dsub cable</t>
+  </si>
+  <si>
+    <t>CABLE DB37M/F DBL SHLD 1'</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/l-com/CS2N37MF-1/21287760</t>
   </si>
 </sst>
 </file>
@@ -534,7 +567,7 @@
   <numFmts count="1">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,13 +608,36 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -597,7 +653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -631,6 +687,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -968,23 +1033,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L58"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.26953125" customWidth="1"/>
-    <col min="7" max="7" width="69.453125" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="69.42578125" customWidth="1"/>
     <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.54296875" customWidth="1"/>
-    <col min="10" max="10" width="62.54296875" customWidth="1"/>
-    <col min="11" max="11" width="55.81640625" customWidth="1"/>
+    <col min="9" max="9" width="83.5703125" customWidth="1"/>
+    <col min="10" max="10" width="62.5703125" customWidth="1"/>
+    <col min="11" max="11" width="55.85546875" customWidth="1"/>
     <col min="12" max="12" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1022,7 +1087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1046,7 +1111,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -1060,7 +1125,7 @@
         <v>9.99</v>
       </c>
       <c r="E3" s="6">
-        <f t="shared" ref="E3:E43" si="0">C3*D3</f>
+        <f t="shared" ref="E3:E51" si="0">C3*D3</f>
         <v>9.99</v>
       </c>
       <c r="F3" s="6"/>
@@ -1069,7 +1134,7 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1093,7 +1158,7 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1119,7 +1184,7 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -1145,33 +1210,33 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="13">
         <v>2</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="14">
         <v>1106</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="14">
         <f t="shared" si="0"/>
         <v>2212</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="14"/>
+      <c r="G7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="15" t="s">
         <v>92</v>
       </c>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1193,7 +1258,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>150</v>
       </c>
@@ -1215,7 +1280,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>149</v>
       </c>
@@ -1234,7 +1299,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1323,7 @@
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>157</v>
       </c>
@@ -1283,7 +1348,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>158</v>
       </c>
@@ -1308,7 +1373,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -1331,7 +1396,7 @@
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
@@ -1354,7 +1419,7 @@
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
@@ -1376,7 +1441,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
@@ -1403,7 +1468,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -1426,7 +1491,7 @@
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>50</v>
       </c>
@@ -1449,7 +1514,7 @@
       </c>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>118</v>
       </c>
@@ -1472,7 +1537,7 @@
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>106</v>
       </c>
@@ -1495,7 +1560,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
@@ -1518,7 +1583,7 @@
       </c>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>107</v>
       </c>
@@ -1541,7 +1606,7 @@
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>56</v>
       </c>
@@ -1564,7 +1629,7 @@
       </c>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>59</v>
       </c>
@@ -1587,7 +1652,7 @@
       </c>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>62</v>
       </c>
@@ -1610,7 +1675,7 @@
       </c>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>65</v>
       </c>
@@ -1633,7 +1698,7 @@
       </c>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>105</v>
       </c>
@@ -1656,7 +1721,7 @@
       </c>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>73</v>
       </c>
@@ -1681,7 +1746,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>75</v>
       </c>
@@ -1704,7 +1769,7 @@
       </c>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>77</v>
       </c>
@@ -1727,7 +1792,7 @@
       </c>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>82</v>
       </c>
@@ -1750,7 +1815,7 @@
       </c>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>83</v>
       </c>
@@ -1773,7 +1838,7 @@
       </c>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>86</v>
       </c>
@@ -1796,7 +1861,7 @@
       </c>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>87</v>
       </c>
@@ -1820,7 +1885,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="5"/>
     </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>112</v>
       </c>
@@ -1833,8 +1898,8 @@
       <c r="D36" s="2">
         <v>9.85</v>
       </c>
-      <c r="E36" s="2">
-        <f>C36*D36</f>
+      <c r="E36" s="6">
+        <f t="shared" si="0"/>
         <v>19.7</v>
       </c>
       <c r="F36" s="2"/>
@@ -1842,7 +1907,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>94</v>
       </c>
@@ -1865,7 +1930,7 @@
       </c>
       <c r="H37" s="5"/>
     </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>101</v>
       </c>
@@ -1888,7 +1953,7 @@
       </c>
       <c r="H38" s="5"/>
     </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>103</v>
       </c>
@@ -1911,7 +1976,7 @@
       </c>
       <c r="H39" s="5"/>
     </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>111</v>
       </c>
@@ -1933,7 +1998,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>120</v>
       </c>
@@ -1955,7 +2020,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>123</v>
       </c>
@@ -1968,7 +2033,7 @@
       <c r="D42" s="2">
         <v>299.54000000000002</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="6">
         <f t="shared" si="0"/>
         <v>299.54000000000002</v>
       </c>
@@ -1977,7 +2042,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
@@ -1990,7 +2055,7 @@
       <c r="D43" s="2">
         <v>6.74</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="6">
         <f t="shared" si="0"/>
         <v>13.48</v>
       </c>
@@ -2001,7 +2066,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>132</v>
       </c>
@@ -2014,14 +2079,15 @@
       <c r="D44" s="2">
         <v>15.89</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="6">
+        <f t="shared" si="0"/>
         <v>15.89</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>134</v>
       </c>
@@ -2035,7 +2101,8 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="E45" s="6">
-        <v>12.41</v>
+        <f t="shared" si="0"/>
+        <v>8.2799999999999994</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>137</v>
@@ -2047,7 +2114,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>139</v>
       </c>
@@ -2060,7 +2127,8 @@
       <c r="D46" s="7">
         <v>4.3600000000000003</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="6">
+        <f t="shared" si="0"/>
         <v>4.3600000000000003</v>
       </c>
       <c r="F46" s="6" t="s">
@@ -2071,7 +2139,7 @@
       </c>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>143</v>
       </c>
@@ -2085,6 +2153,7 @@
         <v>2.73</v>
       </c>
       <c r="E47" s="6">
+        <f t="shared" si="0"/>
         <v>2.73</v>
       </c>
       <c r="F47" s="6" t="s">
@@ -2095,7 +2164,7 @@
       </c>
       <c r="H47" s="1"/>
     </row>
-    <row r="48" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>144</v>
       </c>
@@ -2109,6 +2178,7 @@
         <v>1.2</v>
       </c>
       <c r="E48" s="6">
+        <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
       <c r="F48" s="6" t="s">
@@ -2119,33 +2189,154 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="6"/>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7">
+        <v>1414.12</v>
+      </c>
+      <c r="E49" s="6">
+        <f t="shared" si="0"/>
+        <v>1414.12</v>
+      </c>
       <c r="F49" s="6"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="6"/>
+      <c r="G49" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7">
+        <v>7.37</v>
+      </c>
+      <c r="E50" s="6">
+        <f t="shared" si="0"/>
+        <v>7.37</v>
+      </c>
       <c r="F50" s="6"/>
-      <c r="G50" s="1"/>
+      <c r="G50" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D51" s="7" t="s">
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7">
+        <v>108.06</v>
+      </c>
+      <c r="E51" s="6">
+        <f t="shared" si="0"/>
+        <v>108.06</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D58" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E58" s="6">
         <f>SUM(E3:E45)</f>
-        <v>12927.229999999994</v>
+        <v>12923.099999999995</v>
       </c>
     </row>
   </sheetData>
@@ -2197,8 +2388,13 @@
     <hyperlink ref="G12" r:id="rId45" xr:uid="{80AEB9C5-B34A-47B7-B629-CA013D850F78}"/>
     <hyperlink ref="G13" r:id="rId46" xr:uid="{9A7EEE39-F6AF-4441-96F7-8CCFEF7E26ED}"/>
     <hyperlink ref="G42" r:id="rId47" display="https://www.ebay.com/itm/405898925209?_skw=Kamoer+DIP+1500+Peristaltic+Pumps&amp;itmmeta=01K6KVSWHYJSNG6EA2PQ3BRXEZ&amp;hash=item5e81761499:g:dY8AAOSwmIxoNAUL&amp;itmprp=enc%3AAQAKAAABAFkggFvd1GGDu0w3yXCmi1eeCrwe9QRSEREaUrIDNQcHl2ejBZQd5g5QB4ibtDoehHyRqDUYqWekcvHA4F8PR7E4WfwqcKy%2F6B4jPy%2FdKyfrsZRcKMvBMQJ0wUJKbUB2TtMjOIE2fbYT57uDx6QoXwzDzwwx%2FTiMCwI4NXQ%2Fzk49ElZpUG4mNZ95YLSdIfqhh9EBUlo3RaabFdrQbfIU5mbzxX3Dbw%2FVQ1r1sdAODMwUPvMVsTSBN22hor5VFIwmemSIFqdIGv228Z4PCNOkRGZ5PEv0usP2Il2KKxlkIroaNF4EwcXdTXt4XJ8U9s9J25WHt4%2BWj2ZfYeQipRKgxRI%3D%7Ctkp%3ABFBMlsnn-7Rm" xr:uid="{D6E43660-0348-48F7-B835-5FFA92D0AC06}"/>
+    <hyperlink ref="H49" r:id="rId48" xr:uid="{AFA37929-80FF-4637-AB25-F765C59DEC80}"/>
+    <hyperlink ref="G49" r:id="rId49" location="783729-01" xr:uid="{86E4315F-9605-4390-9808-4C1319284FB5}"/>
+    <hyperlink ref="I49" r:id="rId50" xr:uid="{0D945760-6966-49BB-81FD-0CCA53C54EE4}"/>
+    <hyperlink ref="G50" r:id="rId51" xr:uid="{A22DF26B-12AE-4EE4-BB05-EE40FB1AEBE2}"/>
+    <hyperlink ref="G51" r:id="rId52" xr:uid="{2FFE435A-D60B-4786-9A2A-8172F6B1C65F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId48"/>
+  <pageSetup orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>
--- a/variations/Camden/V0.2.2/BOM-SPARC-Camden-V0.2.2.xlsx
+++ b/variations/Camden/V0.2.2/BOM-SPARC-Camden-V0.2.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Smart-Pack-for-Advanced-Research-and-Control\variations\Camden\V0.2.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C02FDF-E677-4CCF-B93B-DF51A371EF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2422D35-C0EE-4BF7-8AD9-798488D44856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="177">
   <si>
     <t>Total Cost</t>
   </si>
@@ -558,6 +558,15 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/l-com/CS2N37MF-1/21287760</t>
+  </si>
+  <si>
+    <t>MFR Part Number</t>
+  </si>
+  <si>
+    <t>Strain Gauge Glue (cheap option)</t>
+  </si>
+  <si>
+    <t>This is the low-cost option, and we should not really use it.</t>
   </si>
 </sst>
 </file>
@@ -1033,23 +1042,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="69.42578125" customWidth="1"/>
-    <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.5703125" customWidth="1"/>
-    <col min="10" max="10" width="62.5703125" customWidth="1"/>
-    <col min="11" max="11" width="55.85546875" customWidth="1"/>
-    <col min="12" max="12" width="51" customWidth="1"/>
+    <col min="3" max="3" width="74" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="69.42578125" customWidth="1"/>
+    <col min="9" max="9" width="76" customWidth="1"/>
+    <col min="10" max="10" width="83.5703125" customWidth="1"/>
+    <col min="11" max="11" width="62.5703125" customWidth="1"/>
+    <col min="12" max="12" width="55.85546875" customWidth="1"/>
+    <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1057,1344 +1067,1429 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2">
         <v>10</v>
       </c>
-      <c r="D2" s="6">
+      <c r="E2" s="6">
         <v>8.2200000000000006</v>
       </c>
-      <c r="E2" s="6">
-        <f>C2*D2</f>
+      <c r="F2" s="6">
+        <f>D2*E2</f>
         <v>82.2</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
         <v>9.99</v>
       </c>
-      <c r="E3" s="6">
-        <f t="shared" ref="E3:E51" si="0">C3*D3</f>
+      <c r="F3" s="6">
+        <f t="shared" ref="F3:F52" si="0">D3*E3</f>
         <v>9.99</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
         <v>234.98</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <f t="shared" si="0"/>
         <v>234.98</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
         <v>3427</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <f t="shared" si="0"/>
         <v>3427</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
         <v>3048</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <f t="shared" si="0"/>
         <v>3048</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="13"/>
+      <c r="D7" s="13">
         <v>2</v>
       </c>
-      <c r="D7" s="14">
+      <c r="E7" s="14">
         <v>1106</v>
       </c>
-      <c r="E7" s="14">
+      <c r="F7" s="14">
         <f t="shared" si="0"/>
         <v>2212</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14"/>
+      <c r="H7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="I7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
         <v>56.97</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>56.97</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="11"/>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6">
         <v>10.72</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>10.72</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="6"/>
+      <c r="H9" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="6">
-        <v>10.72</v>
-      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="2"/>
       <c r="E10" s="6">
         <v>10.72</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="3" t="s">
+      <c r="F10" s="6">
+        <v>10.72</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6">
         <v>90.99</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
         <v>90.99</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="6"/>
+      <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6">
         <v>162.72</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>162.72</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="6"/>
+      <c r="H12" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5"/>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
         <v>162.72</v>
       </c>
-      <c r="E13" s="6">
-        <f t="shared" ref="E13" si="1">C13*D13</f>
+      <c r="F13" s="6">
+        <f t="shared" ref="F13" si="1">D13*E13</f>
         <v>162.72</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="6"/>
+      <c r="H13" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
         <v>2</v>
       </c>
-      <c r="D14" s="6">
+      <c r="E14" s="6">
         <v>23.08</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>46.16</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="6"/>
+      <c r="H14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="5"/>
+      <c r="D15" s="2">
         <v>2</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="6">
         <v>7.26</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
         <v>14.52</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="6"/>
+      <c r="H15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6">
         <v>8.98</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="6">
         <f t="shared" si="0"/>
         <v>8.98</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6">
+        <v>8.98</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" ref="F17" si="2">D17*E17</f>
+        <v>8.98</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="D17" s="6">
+      <c r="E18" s="6">
         <v>74.89</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F18" s="6">
         <f t="shared" si="0"/>
         <v>149.78</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="3" t="s">
+      <c r="G18" s="6"/>
+      <c r="H18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="D18" s="6">
+      <c r="E19" s="6">
         <v>10.17</v>
       </c>
-      <c r="E18" s="6">
-        <f>C18*D18</f>
+      <c r="F19" s="6">
+        <f>D19*E19</f>
         <v>20.34</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="3" t="s">
+      <c r="G19" s="6"/>
+      <c r="H19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
         <v>8</v>
       </c>
-      <c r="D19" s="6">
+      <c r="E20" s="6">
         <v>1.77</v>
       </c>
-      <c r="E19" s="6">
+      <c r="F20" s="6">
         <f t="shared" si="0"/>
         <v>14.16</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="3" t="s">
+      <c r="G20" s="6"/>
+      <c r="H20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2">
         <v>2</v>
       </c>
-      <c r="D20" s="6">
+      <c r="E21" s="6">
         <v>23.66</v>
       </c>
-      <c r="E20" s="6">
+      <c r="F21" s="6">
         <f t="shared" si="0"/>
         <v>47.32</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="3" t="s">
+      <c r="G21" s="6"/>
+      <c r="H21" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6">
         <v>15.02</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F22" s="6">
         <f t="shared" si="0"/>
         <v>15.02</v>
       </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="3" t="s">
+      <c r="G22" s="6"/>
+      <c r="H22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
         <v>12.46</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F23" s="6">
         <f t="shared" si="0"/>
         <v>12.46</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="3" t="s">
+      <c r="G23" s="6"/>
+      <c r="H23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6">
         <v>15.13</v>
       </c>
-      <c r="E23" s="6">
+      <c r="F24" s="6">
         <f t="shared" si="0"/>
         <v>15.13</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="3" t="s">
+      <c r="G24" s="6"/>
+      <c r="H24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6">
         <v>29.3</v>
       </c>
-      <c r="E24" s="6">
+      <c r="F25" s="6">
         <f t="shared" si="0"/>
         <v>29.3</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="3" t="s">
+      <c r="G25" s="6"/>
+      <c r="H25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6">
         <v>4.09</v>
       </c>
-      <c r="E25" s="6">
+      <c r="F26" s="6">
         <f t="shared" si="0"/>
         <v>4.09</v>
       </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="3" t="s">
+      <c r="G26" s="6"/>
+      <c r="H26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6">
         <v>147.52000000000001</v>
       </c>
-      <c r="E26" s="6">
+      <c r="F27" s="6">
         <f t="shared" si="0"/>
         <v>147.52000000000001</v>
       </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="3" t="s">
+      <c r="G27" s="6"/>
+      <c r="H27" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2">
         <v>4</v>
       </c>
-      <c r="D27" s="6">
+      <c r="E28" s="6">
         <v>1.45</v>
       </c>
-      <c r="E27" s="6">
+      <c r="F28" s="6">
         <f t="shared" si="0"/>
         <v>5.8</v>
       </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="3" t="s">
+      <c r="G28" s="6"/>
+      <c r="H28" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
         <v>1.46</v>
       </c>
-      <c r="E28" s="6">
+      <c r="F29" s="6">
         <f t="shared" si="0"/>
         <v>1.46</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="3" t="s">
+      <c r="G29" s="6"/>
+      <c r="H29" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="2">
-        <v>1</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6">
         <v>2195</v>
       </c>
-      <c r="E29" s="6">
+      <c r="F30" s="6">
         <f t="shared" si="0"/>
         <v>2195</v>
       </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="3" t="s">
+      <c r="G30" s="6"/>
+      <c r="H30" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="2">
-        <v>1</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
         <v>99.89</v>
       </c>
-      <c r="E30" s="6">
+      <c r="F31" s="6">
         <f t="shared" si="0"/>
         <v>99.89</v>
       </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="3" t="s">
+      <c r="G31" s="6"/>
+      <c r="H31" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
         <v>10</v>
       </c>
-      <c r="D31" s="6">
+      <c r="E32" s="6">
         <v>6.92</v>
       </c>
-      <c r="E31" s="6">
+      <c r="F32" s="6">
         <f t="shared" si="0"/>
         <v>69.2</v>
       </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="3" t="s">
+      <c r="G32" s="6"/>
+      <c r="H32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2">
         <v>2</v>
       </c>
-      <c r="D32" s="7">
+      <c r="E33" s="7">
         <v>72.75</v>
       </c>
-      <c r="E32" s="6">
+      <c r="F33" s="6">
         <f t="shared" si="0"/>
         <v>145.5</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="3" t="s">
+      <c r="G33" s="6"/>
+      <c r="H33" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C34" s="5"/>
+      <c r="D34" s="2">
         <v>5</v>
       </c>
-      <c r="D33" s="6">
+      <c r="E34" s="6">
         <v>3.44</v>
       </c>
-      <c r="E33" s="6">
+      <c r="F34" s="6">
         <f t="shared" si="0"/>
         <v>17.2</v>
       </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="3" t="s">
+      <c r="G34" s="6"/>
+      <c r="H34" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2">
         <v>2</v>
       </c>
-      <c r="D34" s="6">
+      <c r="E35" s="6">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E34" s="6">
+      <c r="F35" s="6">
         <f t="shared" si="0"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="3" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="2">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6">
         <v>14.65</v>
       </c>
-      <c r="E35" s="6">
+      <c r="F36" s="6">
         <f t="shared" si="0"/>
         <v>14.65</v>
       </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="3" t="s">
+      <c r="G36" s="6"/>
+      <c r="H36" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="5"/>
-    </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="I36" s="3"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2">
         <v>2</v>
       </c>
-      <c r="D36" s="2">
+      <c r="E37" s="2">
         <v>9.85</v>
       </c>
-      <c r="E36" s="6">
+      <c r="F37" s="6">
         <f t="shared" si="0"/>
         <v>19.7</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="8" t="s">
+      <c r="G37" s="2"/>
+      <c r="H37" s="8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="2">
-        <v>1</v>
-      </c>
-      <c r="D37" s="6">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6">
         <v>19.989999999999998</v>
       </c>
-      <c r="E37" s="6">
+      <c r="F38" s="6">
         <f t="shared" si="0"/>
         <v>19.989999999999998</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="3" t="s">
+      <c r="G38" s="6"/>
+      <c r="H38" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="6">
+      <c r="C39" s="5"/>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6">
         <v>1.87</v>
       </c>
-      <c r="E38" s="6">
+      <c r="F39" s="6">
         <f t="shared" si="0"/>
         <v>1.87</v>
       </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="3" t="s">
+      <c r="G39" s="6"/>
+      <c r="H39" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="2">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6">
         <v>22.56</v>
       </c>
-      <c r="E39" s="6">
+      <c r="F40" s="6">
         <f t="shared" si="0"/>
         <v>22.56</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="3" t="s">
+      <c r="G40" s="6"/>
+      <c r="H40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H39" s="5"/>
-    </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2">
         <v>2</v>
       </c>
-      <c r="D40" s="2">
+      <c r="E41" s="2">
         <v>2.1</v>
       </c>
-      <c r="E40" s="6">
+      <c r="F41" s="6">
         <f t="shared" si="0"/>
         <v>4.2</v>
       </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="3" t="s">
+      <c r="G41" s="6"/>
+      <c r="H41" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2">
         <v>4</v>
       </c>
-      <c r="D41" s="6">
+      <c r="E42" s="6">
         <v>3.75</v>
       </c>
-      <c r="E41" s="6">
+      <c r="F42" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="1" t="s">
+      <c r="G42" s="6"/>
+      <c r="H42" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="2">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2">
+      <c r="C43" s="2"/>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2">
         <v>299.54000000000002</v>
       </c>
-      <c r="E42" s="6">
+      <c r="F43" s="6">
         <f t="shared" si="0"/>
         <v>299.54000000000002</v>
       </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="8" t="s">
+      <c r="G43" s="2"/>
+      <c r="H43" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2">
         <v>2</v>
       </c>
-      <c r="D43" s="2">
+      <c r="E44" s="2">
         <v>6.74</v>
       </c>
-      <c r="E43" s="6">
+      <c r="F44" s="6">
         <f t="shared" si="0"/>
         <v>13.48</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="2">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2">
         <v>15.89</v>
       </c>
-      <c r="E44" s="6">
+      <c r="F45" s="6">
         <f t="shared" si="0"/>
         <v>15.89</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2">
         <v>4</v>
       </c>
-      <c r="D45" s="7">
+      <c r="E46" s="7">
         <v>2.0699999999999998</v>
       </c>
-      <c r="E45" s="6">
+      <c r="F46" s="6">
         <f t="shared" si="0"/>
         <v>8.2799999999999994</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="G46" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7">
         <v>4.3600000000000003</v>
       </c>
-      <c r="E46" s="6">
+      <c r="F47" s="6">
         <f t="shared" si="0"/>
         <v>4.3600000000000003</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="G47" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C47" s="2">
-        <v>1</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C48" s="10"/>
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7">
         <v>2.73</v>
       </c>
-      <c r="E47" s="6">
+      <c r="F48" s="6">
         <f t="shared" si="0"/>
         <v>2.73</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="G48" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B49" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="C49" s="9"/>
+      <c r="D49" s="2">
+        <v>1</v>
+      </c>
+      <c r="E49" s="7">
         <v>1.2</v>
       </c>
-      <c r="E48" s="6">
+      <c r="F49" s="6">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="G49" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C49" s="2">
-        <v>1</v>
-      </c>
-      <c r="D49" s="7">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2">
+        <v>1</v>
+      </c>
+      <c r="E50" s="7">
         <v>1414.12</v>
       </c>
-      <c r="E49" s="6">
+      <c r="F50" s="6">
         <f t="shared" si="0"/>
         <v>1414.12</v>
       </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="1" t="s">
+      <c r="G50" s="6"/>
+      <c r="H50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="J50" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C50" s="2">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7">
+      <c r="C51" s="5"/>
+      <c r="D51" s="2">
+        <v>1</v>
+      </c>
+      <c r="E51" s="7">
         <v>7.37</v>
       </c>
-      <c r="E50" s="6">
+      <c r="F51" s="6">
         <f t="shared" si="0"/>
         <v>7.37</v>
       </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="1" t="s">
+      <c r="G51" s="6"/>
+      <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B52" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C51" s="2">
-        <v>1</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="C52" s="5"/>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="7">
         <v>108.06</v>
       </c>
-      <c r="E51" s="6">
+      <c r="F52" s="6">
         <f t="shared" si="0"/>
         <v>108.06</v>
       </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="1" t="s">
+      <c r="G52" s="6"/>
+      <c r="H52" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="6"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="7"/>
       <c r="F53" s="6"/>
-      <c r="G53" s="1"/>
+      <c r="G53" s="6"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="6"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="7"/>
       <c r="F54" s="6"/>
-      <c r="G54" s="1"/>
+      <c r="G54" s="6"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="6"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="7"/>
       <c r="F55" s="6"/>
-      <c r="G55" s="1"/>
+      <c r="G55" s="6"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="6"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="7"/>
       <c r="F56" s="6"/>
-      <c r="G56" s="1"/>
+      <c r="G56" s="6"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="6"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="7"/>
       <c r="F57" s="6"/>
-      <c r="G57" s="1"/>
+      <c r="G57" s="6"/>
       <c r="H57" s="1"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D58" s="7" t="s">
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E59" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="6">
-        <f>SUM(E3:E45)</f>
-        <v>12923.099999999995</v>
+      <c r="F59" s="6">
+        <f>SUM(F3:F46)</f>
+        <v>12932.079999999994</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{FC65F728-1D6C-4930-9736-CD308A81A115}"/>
-    <hyperlink ref="G4" r:id="rId2" xr:uid="{3FA92BB8-87CB-48DF-80DE-ADB99C5948DA}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{2B925F9B-9EBC-46F8-92CC-B2D2295D9E04}"/>
-    <hyperlink ref="G6" r:id="rId4" xr:uid="{D7748C9A-D5A9-4091-9C5F-1C78524E3FEB}"/>
-    <hyperlink ref="G8" r:id="rId5" xr:uid="{BE59E38F-DA22-4ED1-BF36-E84DE0018044}"/>
-    <hyperlink ref="G7" r:id="rId6" xr:uid="{843281D0-FA21-4F36-A652-0F07141A7B84}"/>
-    <hyperlink ref="G3" r:id="rId7" xr:uid="{AC5FA834-82E0-404E-B150-C4F68DA38C6A}"/>
-    <hyperlink ref="G11" r:id="rId8" xr:uid="{30A401D7-C620-43B9-9D9E-19B3DC7BF553}"/>
-    <hyperlink ref="H12" r:id="rId9" xr:uid="{9E7C13BC-99F6-4C00-8247-D65DF4039E02}"/>
-    <hyperlink ref="G15" r:id="rId10" xr:uid="{D9870AF0-1C4B-473B-8416-474E754D5E7E}"/>
-    <hyperlink ref="G16" r:id="rId11" xr:uid="{7E2805CC-0B04-4DB0-9F38-3741F75A7D1D}"/>
-    <hyperlink ref="G17" r:id="rId12" xr:uid="{6AF56708-0BAB-42E8-A3AE-FD431334CF6C}"/>
-    <hyperlink ref="G18" r:id="rId13" xr:uid="{F2324ACB-C085-42C4-8640-3C360A4D119E}"/>
-    <hyperlink ref="G21" r:id="rId14" xr:uid="{36F5D6E3-807C-49A7-8D30-80566D9949D4}"/>
-    <hyperlink ref="G23" r:id="rId15" xr:uid="{1F94BCB9-4D2C-4C92-8BF0-A4FC479E37E8}"/>
-    <hyperlink ref="G24" r:id="rId16" xr:uid="{6624F982-B428-4251-AA28-31179DCD8937}"/>
-    <hyperlink ref="G25" r:id="rId17" xr:uid="{58E2A489-0714-4655-8748-622D874EF6F8}"/>
-    <hyperlink ref="G26" r:id="rId18" xr:uid="{81E87505-E60E-4515-89EA-9361938F7388}"/>
-    <hyperlink ref="G27" r:id="rId19" xr:uid="{EFDA772F-CC83-4998-A756-1FADE307C734}"/>
-    <hyperlink ref="G28" r:id="rId20" xr:uid="{F81462CE-4E7C-4FAB-8A8E-D305901B6FCF}"/>
-    <hyperlink ref="G31" r:id="rId21" xr:uid="{0B3AB74B-6B3E-4207-9645-7AB7D6617AD3}"/>
-    <hyperlink ref="G32" r:id="rId22" xr:uid="{5CF86D47-7D87-4635-9306-B8490C771687}"/>
-    <hyperlink ref="G34" r:id="rId23" xr:uid="{71E7E2F7-3EA3-469E-BDBD-A5E1E2E4F347}"/>
-    <hyperlink ref="G35" r:id="rId24" xr:uid="{F2165E25-79D9-4521-9261-0FF86CB8CEB1}"/>
-    <hyperlink ref="G14" r:id="rId25" xr:uid="{2459F536-6BF7-4F95-8ED6-65EBE68E0306}"/>
-    <hyperlink ref="H6" r:id="rId26" xr:uid="{A8C35020-1C53-4073-BE6C-0F6933CB1921}"/>
-    <hyperlink ref="H5" r:id="rId27" xr:uid="{A49999D0-0D24-4148-A259-6949303F3996}"/>
-    <hyperlink ref="H7" r:id="rId28" xr:uid="{D90F92BC-9947-4813-8C28-6009DA178051}"/>
-    <hyperlink ref="G29" r:id="rId29" xr:uid="{F3415021-EB69-4CB6-B212-558D2454FF2B}"/>
-    <hyperlink ref="H29" r:id="rId30" xr:uid="{E4EF5DF5-36DD-4B50-AF25-A19F9CE4857A}"/>
-    <hyperlink ref="G38" r:id="rId31" display="https://www.digikey.com/en/products/detail/io-audio-technologies/IO-C14SP-63/21379594?gad_source=1&amp;gad_campaignid=22396809060&amp;gbraid=0AAAAADrbLlisC8UtMjpExL2rbCWoG3ieR&amp;gclid=Cj0KCQjw0NPGBhCDARIsAGAzpp2VLlJaqhBiZUHDGRJcszbohHTDT2yecNaX-w7lJU8lPrGXw1UWNiwaAsExEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{4B8089ED-EC5B-48CB-8DCC-6C3B9EB37FA7}"/>
-    <hyperlink ref="G39" r:id="rId32" xr:uid="{E263962D-47C1-49F9-A559-36360176D757}"/>
-    <hyperlink ref="G19" r:id="rId33" xr:uid="{83A27BB2-9C4A-4120-9925-FBAA61079743}"/>
-    <hyperlink ref="G36" r:id="rId34" xr:uid="{1E1A9060-9FD1-40EB-9CB4-035E777CB97F}"/>
-    <hyperlink ref="G20" r:id="rId35" xr:uid="{E3301FAD-92C1-4805-8EF6-30AE4F47746A}"/>
-    <hyperlink ref="G41" r:id="rId36" xr:uid="{94087BF9-485B-4DE1-AA9E-568F4259E676}"/>
-    <hyperlink ref="G43" r:id="rId37" xr:uid="{6D79D5B6-03CD-4FCF-94AD-8DF566E11950}"/>
-    <hyperlink ref="G44" r:id="rId38" display="https://nam02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.grainger.com%2Fproduct%2FMILWAUKEE-Hole-Saw-1-in-Saw-Dia-856EV8&amp;data=05%7C02%7CCKB11%40email.sc.edu%7C9a1df447a7c2434dc85d08de157fc0b4%7C4b2a4b19d135420e8bb2b1cd238998cc%7C0%7C0%7C638971835598967940%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=EAjn5hwuV%2BewMqz9WyyZN%2Fqwh4VRByeEbQ3Le73uExc%3D&amp;reserved=0" xr:uid="{A9796287-2762-473D-888E-E0F37F2D5222}"/>
-    <hyperlink ref="H45" r:id="rId39" xr:uid="{B771626B-BE96-4E86-B8E7-5F4D421B11CC}"/>
-    <hyperlink ref="G30" r:id="rId40" xr:uid="{9087F97E-6A29-4916-9C63-C220AC3B6655}"/>
-    <hyperlink ref="G40" r:id="rId41" xr:uid="{3FA6174D-CFA4-4F51-8AB7-928DB84B83AE}"/>
-    <hyperlink ref="G10" r:id="rId42" xr:uid="{CA460F6E-5DB5-4664-8FEE-75CFFB393BB3}"/>
-    <hyperlink ref="G33" r:id="rId43" xr:uid="{FCA7462C-56B8-40BE-88B0-4E17914E262A}"/>
-    <hyperlink ref="H13" r:id="rId44" xr:uid="{6182DCE3-4B59-424F-BBA5-94FF6A050AA7}"/>
-    <hyperlink ref="G12" r:id="rId45" xr:uid="{80AEB9C5-B34A-47B7-B629-CA013D850F78}"/>
-    <hyperlink ref="G13" r:id="rId46" xr:uid="{9A7EEE39-F6AF-4441-96F7-8CCFEF7E26ED}"/>
-    <hyperlink ref="G42" r:id="rId47" display="https://www.ebay.com/itm/405898925209?_skw=Kamoer+DIP+1500+Peristaltic+Pumps&amp;itmmeta=01K6KVSWHYJSNG6EA2PQ3BRXEZ&amp;hash=item5e81761499:g:dY8AAOSwmIxoNAUL&amp;itmprp=enc%3AAQAKAAABAFkggFvd1GGDu0w3yXCmi1eeCrwe9QRSEREaUrIDNQcHl2ejBZQd5g5QB4ibtDoehHyRqDUYqWekcvHA4F8PR7E4WfwqcKy%2F6B4jPy%2FdKyfrsZRcKMvBMQJ0wUJKbUB2TtMjOIE2fbYT57uDx6QoXwzDzwwx%2FTiMCwI4NXQ%2Fzk49ElZpUG4mNZ95YLSdIfqhh9EBUlo3RaabFdrQbfIU5mbzxX3Dbw%2FVQ1r1sdAODMwUPvMVsTSBN22hor5VFIwmemSIFqdIGv228Z4PCNOkRGZ5PEv0usP2Il2KKxlkIroaNF4EwcXdTXt4XJ8U9s9J25WHt4%2BWj2ZfYeQipRKgxRI%3D%7Ctkp%3ABFBMlsnn-7Rm" xr:uid="{D6E43660-0348-48F7-B835-5FFA92D0AC06}"/>
-    <hyperlink ref="H49" r:id="rId48" xr:uid="{AFA37929-80FF-4637-AB25-F765C59DEC80}"/>
-    <hyperlink ref="G49" r:id="rId49" location="783729-01" xr:uid="{86E4315F-9605-4390-9808-4C1319284FB5}"/>
-    <hyperlink ref="I49" r:id="rId50" xr:uid="{0D945760-6966-49BB-81FD-0CCA53C54EE4}"/>
-    <hyperlink ref="G50" r:id="rId51" xr:uid="{A22DF26B-12AE-4EE4-BB05-EE40FB1AEBE2}"/>
-    <hyperlink ref="G51" r:id="rId52" xr:uid="{2FFE435A-D60B-4786-9A2A-8172F6B1C65F}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{FC65F728-1D6C-4930-9736-CD308A81A115}"/>
+    <hyperlink ref="H4" r:id="rId2" xr:uid="{3FA92BB8-87CB-48DF-80DE-ADB99C5948DA}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{2B925F9B-9EBC-46F8-92CC-B2D2295D9E04}"/>
+    <hyperlink ref="H6" r:id="rId4" xr:uid="{D7748C9A-D5A9-4091-9C5F-1C78524E3FEB}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{BE59E38F-DA22-4ED1-BF36-E84DE0018044}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{843281D0-FA21-4F36-A652-0F07141A7B84}"/>
+    <hyperlink ref="H3" r:id="rId7" xr:uid="{AC5FA834-82E0-404E-B150-C4F68DA38C6A}"/>
+    <hyperlink ref="H11" r:id="rId8" xr:uid="{30A401D7-C620-43B9-9D9E-19B3DC7BF553}"/>
+    <hyperlink ref="I12" r:id="rId9" xr:uid="{9E7C13BC-99F6-4C00-8247-D65DF4039E02}"/>
+    <hyperlink ref="H15" r:id="rId10" xr:uid="{D9870AF0-1C4B-473B-8416-474E754D5E7E}"/>
+    <hyperlink ref="H16" r:id="rId11" xr:uid="{7E2805CC-0B04-4DB0-9F38-3741F75A7D1D}"/>
+    <hyperlink ref="H18" r:id="rId12" xr:uid="{6AF56708-0BAB-42E8-A3AE-FD431334CF6C}"/>
+    <hyperlink ref="H19" r:id="rId13" xr:uid="{F2324ACB-C085-42C4-8640-3C360A4D119E}"/>
+    <hyperlink ref="H22" r:id="rId14" xr:uid="{36F5D6E3-807C-49A7-8D30-80566D9949D4}"/>
+    <hyperlink ref="H24" r:id="rId15" xr:uid="{1F94BCB9-4D2C-4C92-8BF0-A4FC479E37E8}"/>
+    <hyperlink ref="H25" r:id="rId16" xr:uid="{6624F982-B428-4251-AA28-31179DCD8937}"/>
+    <hyperlink ref="H26" r:id="rId17" xr:uid="{58E2A489-0714-4655-8748-622D874EF6F8}"/>
+    <hyperlink ref="H27" r:id="rId18" xr:uid="{81E87505-E60E-4515-89EA-9361938F7388}"/>
+    <hyperlink ref="H28" r:id="rId19" xr:uid="{EFDA772F-CC83-4998-A756-1FADE307C734}"/>
+    <hyperlink ref="H29" r:id="rId20" xr:uid="{F81462CE-4E7C-4FAB-8A8E-D305901B6FCF}"/>
+    <hyperlink ref="H32" r:id="rId21" xr:uid="{0B3AB74B-6B3E-4207-9645-7AB7D6617AD3}"/>
+    <hyperlink ref="H33" r:id="rId22" xr:uid="{5CF86D47-7D87-4635-9306-B8490C771687}"/>
+    <hyperlink ref="H35" r:id="rId23" xr:uid="{71E7E2F7-3EA3-469E-BDBD-A5E1E2E4F347}"/>
+    <hyperlink ref="H36" r:id="rId24" xr:uid="{F2165E25-79D9-4521-9261-0FF86CB8CEB1}"/>
+    <hyperlink ref="H14" r:id="rId25" xr:uid="{2459F536-6BF7-4F95-8ED6-65EBE68E0306}"/>
+    <hyperlink ref="I6" r:id="rId26" xr:uid="{A8C35020-1C53-4073-BE6C-0F6933CB1921}"/>
+    <hyperlink ref="I5" r:id="rId27" xr:uid="{A49999D0-0D24-4148-A259-6949303F3996}"/>
+    <hyperlink ref="I7" r:id="rId28" xr:uid="{D90F92BC-9947-4813-8C28-6009DA178051}"/>
+    <hyperlink ref="H30" r:id="rId29" xr:uid="{F3415021-EB69-4CB6-B212-558D2454FF2B}"/>
+    <hyperlink ref="I30" r:id="rId30" xr:uid="{E4EF5DF5-36DD-4B50-AF25-A19F9CE4857A}"/>
+    <hyperlink ref="H39" r:id="rId31" display="https://www.digikey.com/en/products/detail/io-audio-technologies/IO-C14SP-63/21379594?gad_source=1&amp;gad_campaignid=22396809060&amp;gbraid=0AAAAADrbLlisC8UtMjpExL2rbCWoG3ieR&amp;gclid=Cj0KCQjw0NPGBhCDARIsAGAzpp2VLlJaqhBiZUHDGRJcszbohHTDT2yecNaX-w7lJU8lPrGXw1UWNiwaAsExEALw_wcB&amp;gclsrc=aw.ds" xr:uid="{4B8089ED-EC5B-48CB-8DCC-6C3B9EB37FA7}"/>
+    <hyperlink ref="H40" r:id="rId32" xr:uid="{E263962D-47C1-49F9-A559-36360176D757}"/>
+    <hyperlink ref="H20" r:id="rId33" xr:uid="{83A27BB2-9C4A-4120-9925-FBAA61079743}"/>
+    <hyperlink ref="H37" r:id="rId34" xr:uid="{1E1A9060-9FD1-40EB-9CB4-035E777CB97F}"/>
+    <hyperlink ref="H21" r:id="rId35" xr:uid="{E3301FAD-92C1-4805-8EF6-30AE4F47746A}"/>
+    <hyperlink ref="H42" r:id="rId36" xr:uid="{94087BF9-485B-4DE1-AA9E-568F4259E676}"/>
+    <hyperlink ref="H44" r:id="rId37" xr:uid="{6D79D5B6-03CD-4FCF-94AD-8DF566E11950}"/>
+    <hyperlink ref="H45" r:id="rId38" display="https://nam02.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.grainger.com%2Fproduct%2FMILWAUKEE-Hole-Saw-1-in-Saw-Dia-856EV8&amp;data=05%7C02%7CCKB11%40email.sc.edu%7C9a1df447a7c2434dc85d08de157fc0b4%7C4b2a4b19d135420e8bb2b1cd238998cc%7C0%7C0%7C638971835598967940%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=EAjn5hwuV%2BewMqz9WyyZN%2Fqwh4VRByeEbQ3Le73uExc%3D&amp;reserved=0" xr:uid="{A9796287-2762-473D-888E-E0F37F2D5222}"/>
+    <hyperlink ref="I46" r:id="rId39" xr:uid="{B771626B-BE96-4E86-B8E7-5F4D421B11CC}"/>
+    <hyperlink ref="H31" r:id="rId40" xr:uid="{9087F97E-6A29-4916-9C63-C220AC3B6655}"/>
+    <hyperlink ref="H41" r:id="rId41" xr:uid="{3FA6174D-CFA4-4F51-8AB7-928DB84B83AE}"/>
+    <hyperlink ref="H10" r:id="rId42" xr:uid="{CA460F6E-5DB5-4664-8FEE-75CFFB393BB3}"/>
+    <hyperlink ref="H34" r:id="rId43" xr:uid="{FCA7462C-56B8-40BE-88B0-4E17914E262A}"/>
+    <hyperlink ref="I13" r:id="rId44" xr:uid="{6182DCE3-4B59-424F-BBA5-94FF6A050AA7}"/>
+    <hyperlink ref="H12" r:id="rId45" xr:uid="{80AEB9C5-B34A-47B7-B629-CA013D850F78}"/>
+    <hyperlink ref="H13" r:id="rId46" xr:uid="{9A7EEE39-F6AF-4441-96F7-8CCFEF7E26ED}"/>
+    <hyperlink ref="H43" r:id="rId47" display="https://www.ebay.com/itm/405898925209?_skw=Kamoer+DIP+1500+Peristaltic+Pumps&amp;itmmeta=01K6KVSWHYJSNG6EA2PQ3BRXEZ&amp;hash=item5e81761499:g:dY8AAOSwmIxoNAUL&amp;itmprp=enc%3AAQAKAAABAFkggFvd1GGDu0w3yXCmi1eeCrwe9QRSEREaUrIDNQcHl2ejBZQd5g5QB4ibtDoehHyRqDUYqWekcvHA4F8PR7E4WfwqcKy%2F6B4jPy%2FdKyfrsZRcKMvBMQJ0wUJKbUB2TtMjOIE2fbYT57uDx6QoXwzDzwwx%2FTiMCwI4NXQ%2Fzk49ElZpUG4mNZ95YLSdIfqhh9EBUlo3RaabFdrQbfIU5mbzxX3Dbw%2FVQ1r1sdAODMwUPvMVsTSBN22hor5VFIwmemSIFqdIGv228Z4PCNOkRGZ5PEv0usP2Il2KKxlkIroaNF4EwcXdTXt4XJ8U9s9J25WHt4%2BWj2ZfYeQipRKgxRI%3D%7Ctkp%3ABFBMlsnn-7Rm" xr:uid="{D6E43660-0348-48F7-B835-5FFA92D0AC06}"/>
+    <hyperlink ref="I50" r:id="rId48" xr:uid="{AFA37929-80FF-4637-AB25-F765C59DEC80}"/>
+    <hyperlink ref="H50" r:id="rId49" location="783729-01" xr:uid="{86E4315F-9605-4390-9808-4C1319284FB5}"/>
+    <hyperlink ref="J50" r:id="rId50" xr:uid="{0D945760-6966-49BB-81FD-0CCA53C54EE4}"/>
+    <hyperlink ref="H51" r:id="rId51" xr:uid="{A22DF26B-12AE-4EE4-BB05-EE40FB1AEBE2}"/>
+    <hyperlink ref="H52" r:id="rId52" xr:uid="{2FFE435A-D60B-4786-9A2A-8172F6B1C65F}"/>
+    <hyperlink ref="H17" r:id="rId53" xr:uid="{5105D23B-A48B-4DCB-BD98-F0992A3E1B30}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId53"/>
+  <pageSetup orientation="portrait" r:id="rId54"/>
 </worksheet>
 </file>
--- a/variations/Camden/V0.2.2/BOM-SPARC-Camden-V0.2.2.xlsx
+++ b/variations/Camden/V0.2.2/BOM-SPARC-Camden-V0.2.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Smart-Pack-for-Advanced-Research-and-Control\variations\Camden\V0.2.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2422D35-C0EE-4BF7-8AD9-798488D44856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FDD2E4-AECE-4776-8387-6C3DCA8A9E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="187">
   <si>
     <t>Total Cost</t>
   </si>
@@ -567,14 +567,45 @@
   </si>
   <si>
     <t>This is the low-cost option, and we should not really use it.</t>
+  </si>
+  <si>
+    <t>wire duct</t>
+  </si>
+  <si>
+    <t>Thomas &amp; Betts Wiring Duct, 2 × 2 in, 72 in, PVC, Gray</t>
+  </si>
+  <si>
+    <t>TYD2X2WPG6</t>
+  </si>
+  <si>
+    <t>Wide-slot, screw-mount</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/THOMAS-BETTS-Wiring-Duct-2-in-Nom-Wd-53UH84</t>
+  </si>
+  <si>
+    <t>wire duct cover</t>
+  </si>
+  <si>
+    <t>Thomas &amp; Betts Wiring Duct Cover, 2 in, 72 in, PVC, Gray</t>
+  </si>
+  <si>
+    <t>TYD2CPG6</t>
+  </si>
+  <si>
+    <t>Snap-on cover for 2 in wiring duct</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/THOMAS-BETTS-Wiring-Duct-Cover-PVC-53UH87</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -662,7 +693,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -707,6 +738,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1042,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2354,27 +2386,57 @@
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="A53" t="s">
+        <v>177</v>
+      </c>
+      <c r="B53" t="s">
+        <v>178</v>
+      </c>
+      <c r="C53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" s="16">
+        <v>34.1</v>
+      </c>
+      <c r="F53" s="16">
+        <v>34.1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>180</v>
+      </c>
+      <c r="H53" t="s">
+        <v>181</v>
+      </c>
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="A54" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" s="16">
+        <v>13.76</v>
+      </c>
+      <c r="F54" s="16">
+        <v>13.76</v>
+      </c>
+      <c r="G54" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" t="s">
+        <v>186</v>
+      </c>
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -2387,50 +2449,14 @@
       <c r="G55" s="6"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E59" s="7" t="s">
+      <c r="E56" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="6">
-        <f>SUM(F3:F46)</f>
-        <v>12932.079999999994</v>
+      <c r="F56" s="6">
+        <f>SUM(F3:F54)</f>
+        <v>14517.779999999995</v>
       </c>
     </row>
   </sheetData>
